--- a/fx_pipeline/data/gold/marts/excel/gold_currency_movement.xlsx
+++ b/fx_pipeline/data/gold/marts/excel/gold_currency_movement.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,30 +448,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>load_batch_id</t>
+          <t>batch_id</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>endpoint_name</t>
+          <t>previous_rate</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>response_status</t>
+          <t>absolute_movement</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>previous_rate</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>absolute_movement</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>percentage_movement</t>
         </is>
@@ -479,7 +469,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -492,37 +482,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.4245</v>
+        <v>1.439</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1.439</v>
       </c>
       <c r="H2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4245</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -535,37 +517,29 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>1.4361</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>1.439</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
       <c r="H3" t="n">
-        <v>200</v>
+        <v>-0.002900000000000125</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4245</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.01449999999999996</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.017901017901015</v>
+        <v>-0.2015288394718641</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -578,37 +552,29 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>1.4467</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>1.4361</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
       <c r="H4" t="n">
-        <v>200</v>
+        <v>0.01060000000000016</v>
       </c>
       <c r="I4" t="n">
-        <v>1.439</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-0.002900000000000125</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-0.2015288394718641</v>
+        <v>0.7381101594596592</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -621,37 +587,29 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>1.4527</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>1.4467</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
       <c r="H5" t="n">
-        <v>200</v>
+        <v>0.006000000000000005</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4361</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.01060000000000016</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.7381101594596592</v>
+        <v>0.4147369876270135</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -664,37 +622,29 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>1.4577</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>1.4527</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
       <c r="H6" t="n">
-        <v>200</v>
+        <v>0.004999999999999893</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4467</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.006000000000000005</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.4147369876270135</v>
+        <v>0.3441866868589449</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -707,37 +657,29 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>1.4518</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>1.4577</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
       <c r="H7" t="n">
-        <v>200</v>
+        <v>-0.005900000000000016</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4527</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.004999999999999893</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.3441866868589449</v>
+        <v>-0.4047472045002412</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -750,37 +692,29 @@
         </is>
       </c>
       <c r="D8" t="n">
+        <v>1.4381</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>1.4518</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
       <c r="H8" t="n">
-        <v>200</v>
+        <v>-0.01370000000000005</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4577</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-0.005900000000000016</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-0.4047472045002412</v>
+        <v>-0.9436561509849873</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -793,37 +727,29 @@
         </is>
       </c>
       <c r="D9" t="n">
+        <v>1.4552</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>1.4381</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
       <c r="H9" t="n">
-        <v>200</v>
+        <v>0.01710000000000012</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4518</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-0.01370000000000005</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-0.9436561509849873</v>
+        <v>1.189068910367855</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -836,37 +762,29 @@
         </is>
       </c>
       <c r="D10" t="n">
+        <v>1.442</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>1.4552</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
       <c r="H10" t="n">
-        <v>200</v>
+        <v>-0.0132000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4381</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.01710000000000012</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.189068910367855</v>
+        <v>-0.9070918086860981</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -879,37 +797,29 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>1.4171</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>1.442</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
       <c r="H11" t="n">
-        <v>200</v>
+        <v>-0.02489999999999992</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4552</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-0.0132000000000001</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.9070918086860981</v>
+        <v>-1.726768377253809</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -922,37 +832,29 @@
         </is>
       </c>
       <c r="D12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>1.4171</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
       <c r="H12" t="n">
-        <v>200</v>
+        <v>0.002899999999999903</v>
       </c>
       <c r="I12" t="n">
-        <v>1.442</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-0.02489999999999992</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-1.726768377253809</v>
+        <v>0.2046432855832265</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -965,37 +867,29 @@
         </is>
       </c>
       <c r="D13" t="n">
+        <v>1.4141</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
         <v>1.42</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
       <c r="H13" t="n">
-        <v>200</v>
+        <v>-0.005900000000000016</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4171</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.002899999999999903</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.2046432855832265</v>
+        <v>-0.4154929577464801</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1008,37 +902,29 @@
         </is>
       </c>
       <c r="D14" t="n">
+        <v>1.4216</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
         <v>1.4141</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
       <c r="H14" t="n">
-        <v>200</v>
+        <v>0.007500000000000062</v>
       </c>
       <c r="I14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-0.005900000000000016</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-0.4154929577464801</v>
+        <v>0.5303726751997782</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1051,37 +937,29 @@
         </is>
       </c>
       <c r="D15" t="n">
+        <v>1.4041</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
         <v>1.4216</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
       <c r="H15" t="n">
-        <v>200</v>
+        <v>-0.01750000000000007</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4141</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.007500000000000062</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.5303726751997782</v>
+        <v>-1.231007315700624</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1094,37 +972,29 @@
         </is>
       </c>
       <c r="D16" t="n">
+        <v>1.4013</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
         <v>1.4041</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
       <c r="H16" t="n">
-        <v>200</v>
+        <v>-0.002799999999999914</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4216</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-0.01750000000000007</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-1.231007315700624</v>
+        <v>-0.1994159960116739</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1137,37 +1007,29 @@
         </is>
       </c>
       <c r="D17" t="n">
+        <v>1.3941</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
         <v>1.4013</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
       <c r="H17" t="n">
-        <v>200</v>
+        <v>-0.007200000000000095</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4041</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-0.002799999999999914</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-0.1994159960116739</v>
+        <v>-0.5138086062941623</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1180,37 +1042,29 @@
         </is>
       </c>
       <c r="D18" t="n">
+        <v>1.3934</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
         <v>1.3941</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
       <c r="H18" t="n">
-        <v>200</v>
+        <v>-0.0006999999999999229</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4013</v>
-      </c>
-      <c r="J18" t="n">
-        <v>-0.007200000000000095</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-0.5138086062941623</v>
+        <v>-0.05021160605407955</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1223,37 +1077,29 @@
         </is>
       </c>
       <c r="D19" t="n">
+        <v>1.3973</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
         <v>1.3934</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
       <c r="H19" t="n">
-        <v>200</v>
+        <v>0.003900000000000015</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3941</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-0.0006999999999999229</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-0.05021160605407955</v>
+        <v>0.2798909143103211</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46104</v>
+        <v>46133</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1262,36 +1108,28 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>AUD</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.3708</v>
+        <v>1.3957</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1.3973</v>
       </c>
       <c r="H20" t="n">
-        <v>200</v>
+        <v>-0.001600000000000046</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3708</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+        <v>-0.1145065483432367</v>
       </c>
     </row>
     <row r="21">
@@ -1312,29 +1150,21 @@
         <v>1.3749</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1.3749</v>
       </c>
       <c r="H21" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3708</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.004099999999999993</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.2990954187335857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1355,28 +1185,20 @@
         <v>1.3783</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1.3749</v>
       </c>
       <c r="H22" t="n">
-        <v>200</v>
+        <v>0.00340000000000007</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3749</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.00340000000000007</v>
-      </c>
-      <c r="K22" t="n">
         <v>0.2472907120517906</v>
       </c>
     </row>
@@ -1398,28 +1220,20 @@
         <v>1.3835</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1.3783</v>
       </c>
       <c r="H23" t="n">
-        <v>200</v>
+        <v>0.005199999999999871</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3783</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.005199999999999871</v>
-      </c>
-      <c r="K23" t="n">
         <v>0.3772763549299769</v>
       </c>
     </row>
@@ -1441,28 +1255,20 @@
         <v>1.387</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1.3835</v>
       </c>
       <c r="H24" t="n">
-        <v>200</v>
+        <v>0.003500000000000059</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3835</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.003500000000000059</v>
-      </c>
-      <c r="K24" t="n">
         <v>0.2529815684857288</v>
       </c>
     </row>
@@ -1484,28 +1290,20 @@
         <v>1.3921</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1.387</v>
       </c>
       <c r="H25" t="n">
-        <v>200</v>
+        <v>0.005099999999999882</v>
       </c>
       <c r="I25" t="n">
-        <v>1.387</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.005099999999999882</v>
-      </c>
-      <c r="K25" t="n">
         <v>0.3677000720980449</v>
       </c>
     </row>
@@ -1527,28 +1325,20 @@
         <v>1.3935</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1.3921</v>
       </c>
       <c r="H26" t="n">
-        <v>200</v>
+        <v>0.001400000000000068</v>
       </c>
       <c r="I26" t="n">
-        <v>1.3921</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.001400000000000068</v>
-      </c>
-      <c r="K26" t="n">
         <v>0.1005674879678233</v>
       </c>
     </row>
@@ -1570,28 +1360,20 @@
         <v>1.3894</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1.3935</v>
       </c>
       <c r="H27" t="n">
-        <v>200</v>
+        <v>-0.004099999999999993</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3935</v>
-      </c>
-      <c r="J27" t="n">
-        <v>-0.004099999999999993</v>
-      </c>
-      <c r="K27" t="n">
         <v>-0.2942231790455682</v>
       </c>
     </row>
@@ -1613,28 +1395,20 @@
         <v>1.3909</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1.3894</v>
       </c>
       <c r="H28" t="n">
-        <v>200</v>
+        <v>0.001500000000000057</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3894</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.001500000000000057</v>
-      </c>
-      <c r="K28" t="n">
         <v>0.1079602706204158</v>
       </c>
     </row>
@@ -1656,28 +1430,20 @@
         <v>1.3912</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1.3909</v>
       </c>
       <c r="H29" t="n">
-        <v>200</v>
+        <v>0.000299999999999967</v>
       </c>
       <c r="I29" t="n">
-        <v>1.3909</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.000299999999999967</v>
-      </c>
-      <c r="K29" t="n">
         <v>0.02156876842332065</v>
       </c>
     </row>
@@ -1699,28 +1465,20 @@
         <v>1.386</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1.3912</v>
       </c>
       <c r="H30" t="n">
-        <v>200</v>
+        <v>-0.005200000000000093</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3912</v>
-      </c>
-      <c r="J30" t="n">
-        <v>-0.005200000000000093</v>
-      </c>
-      <c r="K30" t="n">
         <v>-0.3737780333525081</v>
       </c>
     </row>
@@ -1742,28 +1500,20 @@
         <v>1.3843</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1.386</v>
       </c>
       <c r="H31" t="n">
-        <v>200</v>
+        <v>-0.001699999999999813</v>
       </c>
       <c r="I31" t="n">
-        <v>1.386</v>
-      </c>
-      <c r="J31" t="n">
-        <v>-0.001699999999999813</v>
-      </c>
-      <c r="K31" t="n">
         <v>-0.1226551226551091</v>
       </c>
     </row>
@@ -1785,28 +1535,20 @@
         <v>1.3822</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1.3843</v>
       </c>
       <c r="H32" t="n">
-        <v>200</v>
+        <v>-0.002099999999999991</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3843</v>
-      </c>
-      <c r="J32" t="n">
-        <v>-0.002099999999999991</v>
-      </c>
-      <c r="K32" t="n">
         <v>-0.1517012208336337</v>
       </c>
     </row>
@@ -1828,28 +1570,20 @@
         <v>1.3845</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1.3822</v>
       </c>
       <c r="H33" t="n">
-        <v>200</v>
+        <v>0.002299999999999969</v>
       </c>
       <c r="I33" t="n">
-        <v>1.3822</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.002299999999999969</v>
-      </c>
-      <c r="K33" t="n">
         <v>0.1664013890898545</v>
       </c>
     </row>
@@ -1871,28 +1605,20 @@
         <v>1.3758</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1.3845</v>
       </c>
       <c r="H34" t="n">
-        <v>200</v>
+        <v>-0.008700000000000152</v>
       </c>
       <c r="I34" t="n">
-        <v>1.3845</v>
-      </c>
-      <c r="J34" t="n">
-        <v>-0.008700000000000152</v>
-      </c>
-      <c r="K34" t="n">
         <v>-0.628385698808245</v>
       </c>
     </row>
@@ -1914,28 +1640,20 @@
         <v>1.3782</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1.3758</v>
       </c>
       <c r="H35" t="n">
-        <v>200</v>
+        <v>0.00240000000000018</v>
       </c>
       <c r="I35" t="n">
-        <v>1.3758</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.00240000000000018</v>
-      </c>
-      <c r="K35" t="n">
         <v>0.1744439598779023</v>
       </c>
     </row>
@@ -1957,28 +1675,20 @@
         <v>1.3728</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1.3782</v>
       </c>
       <c r="H36" t="n">
-        <v>200</v>
+        <v>-0.005400000000000071</v>
       </c>
       <c r="I36" t="n">
-        <v>1.3782</v>
-      </c>
-      <c r="J36" t="n">
-        <v>-0.005400000000000071</v>
-      </c>
-      <c r="K36" t="n">
         <v>-0.3918154114061871</v>
       </c>
     </row>
@@ -2000,34 +1710,26 @@
         <v>1.3672</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1.3728</v>
       </c>
       <c r="H37" t="n">
-        <v>200</v>
+        <v>-0.005600000000000049</v>
       </c>
       <c r="I37" t="n">
-        <v>1.3728</v>
-      </c>
-      <c r="J37" t="n">
-        <v>-0.005600000000000049</v>
-      </c>
-      <c r="K37" t="n">
         <v>-0.4079254079254115</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46104</v>
+        <v>46132</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2036,41 +1738,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.86237</v>
+        <v>1.3695</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1.3672</v>
       </c>
       <c r="H38" t="n">
-        <v>200</v>
+        <v>0.002299999999999969</v>
       </c>
       <c r="I38" t="n">
-        <v>0.86237</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+        <v>0.1682270333528356</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46105</v>
+        <v>46133</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2079,41 +1773,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.86415</v>
+        <v>1.3657</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1.3695</v>
       </c>
       <c r="H39" t="n">
-        <v>200</v>
+        <v>-0.003800000000000026</v>
       </c>
       <c r="I39" t="n">
-        <v>0.86237</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.001780000000000004</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.2064079223535146</v>
+        <v>-0.2774735304855805</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2126,37 +1812,29 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.86266</v>
+        <v>0.86415</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0.86415</v>
       </c>
       <c r="H40" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.86415</v>
-      </c>
-      <c r="J40" t="n">
-        <v>-0.001489999999999991</v>
-      </c>
-      <c r="K40" t="n">
-        <v>-0.1724237690215809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2169,37 +1847,29 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.86663</v>
+        <v>0.86266</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0.86415</v>
       </c>
       <c r="H41" t="n">
-        <v>200</v>
+        <v>-0.001489999999999991</v>
       </c>
       <c r="I41" t="n">
-        <v>0.86266</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.003970000000000029</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.460204483805906</v>
+        <v>-0.1724237690215809</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2212,37 +1882,29 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.8682800000000001</v>
+        <v>0.86663</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0.86266</v>
       </c>
       <c r="H42" t="n">
-        <v>200</v>
+        <v>0.003970000000000029</v>
       </c>
       <c r="I42" t="n">
-        <v>0.86663</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.00165000000000004</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.1903926704591395</v>
+        <v>0.460204483805906</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46111</v>
+        <v>46108</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2255,37 +1917,29 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.87078</v>
+        <v>0.8682800000000001</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0.86663</v>
       </c>
       <c r="H43" t="n">
-        <v>200</v>
+        <v>0.00165000000000004</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8682800000000001</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.002499999999999947</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.2879255539687597</v>
+        <v>0.1903926704591395</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2298,37 +1952,29 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.86972</v>
+        <v>0.87078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0.8682800000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>200</v>
+        <v>0.002499999999999947</v>
       </c>
       <c r="I44" t="n">
-        <v>0.87078</v>
-      </c>
-      <c r="J44" t="n">
-        <v>-0.00105999999999995</v>
-      </c>
-      <c r="K44" t="n">
-        <v>-0.1217299432692471</v>
+        <v>0.2879255539687597</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46113</v>
+        <v>46112</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2341,37 +1987,29 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.8617</v>
+        <v>0.86972</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0.87078</v>
       </c>
       <c r="H45" t="n">
-        <v>200</v>
+        <v>-0.00105999999999995</v>
       </c>
       <c r="I45" t="n">
-        <v>0.86972</v>
-      </c>
-      <c r="J45" t="n">
-        <v>-0.008020000000000027</v>
-      </c>
-      <c r="K45" t="n">
-        <v>-0.9221358598169557</v>
+        <v>-0.1217299432692471</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46114</v>
+        <v>46113</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2384,37 +2022,29 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.86768</v>
+        <v>0.8617</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0.86972</v>
       </c>
       <c r="H46" t="n">
-        <v>200</v>
+        <v>-0.008020000000000027</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8617</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.005979999999999985</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.6939770221654851</v>
+        <v>-0.9221358598169557</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46119</v>
+        <v>46114</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2427,37 +2057,29 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.86528</v>
+        <v>0.86768</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0.8617</v>
       </c>
       <c r="H47" t="n">
-        <v>200</v>
+        <v>0.005979999999999985</v>
       </c>
       <c r="I47" t="n">
-        <v>0.86768</v>
-      </c>
-      <c r="J47" t="n">
-        <v>-0.002399999999999958</v>
-      </c>
-      <c r="K47" t="n">
-        <v>-0.2765996680803934</v>
+        <v>0.6939770221654851</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46120</v>
+        <v>46119</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2470,37 +2092,29 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.85426</v>
+        <v>0.86528</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0.86768</v>
       </c>
       <c r="H48" t="n">
-        <v>200</v>
+        <v>-0.002399999999999958</v>
       </c>
       <c r="I48" t="n">
-        <v>0.86528</v>
-      </c>
-      <c r="J48" t="n">
-        <v>-0.01102000000000003</v>
-      </c>
-      <c r="K48" t="n">
-        <v>-1.273576183431956</v>
+        <v>-0.2765996680803934</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46121</v>
+        <v>46120</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2513,37 +2127,29 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.8558</v>
+        <v>0.85426</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0.86528</v>
       </c>
       <c r="H49" t="n">
-        <v>200</v>
+        <v>-0.01102000000000003</v>
       </c>
       <c r="I49" t="n">
-        <v>0.85426</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.001539999999999986</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0.180272984805561</v>
+        <v>-1.273576183431956</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46122</v>
+        <v>46121</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2556,37 +2162,29 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.8539</v>
+        <v>0.8558</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0.85426</v>
       </c>
       <c r="H50" t="n">
-        <v>200</v>
+        <v>0.001539999999999986</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8558</v>
-      </c>
-      <c r="J50" t="n">
-        <v>-0.001900000000000013</v>
-      </c>
-      <c r="K50" t="n">
-        <v>-0.2220144893666759</v>
+        <v>0.180272984805561</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>46125</v>
+        <v>46122</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2599,37 +2197,29 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.85587</v>
+        <v>0.8539</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0.8558</v>
       </c>
       <c r="H51" t="n">
-        <v>200</v>
+        <v>-0.001900000000000013</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8539</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.001970000000000027</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0.2307061716828701</v>
+        <v>-0.2220144893666759</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46126</v>
+        <v>46125</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2642,37 +2232,29 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.84796</v>
+        <v>0.85587</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0.8539</v>
       </c>
       <c r="H52" t="n">
-        <v>200</v>
+        <v>0.001970000000000027</v>
       </c>
       <c r="I52" t="n">
-        <v>0.85587</v>
-      </c>
-      <c r="J52" t="n">
-        <v>-0.007909999999999973</v>
-      </c>
-      <c r="K52" t="n">
-        <v>-0.924205778915019</v>
+        <v>0.2307061716828701</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2685,37 +2267,29 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.8489</v>
+        <v>0.84796</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0.85587</v>
       </c>
       <c r="H53" t="n">
-        <v>200</v>
+        <v>-0.007909999999999973</v>
       </c>
       <c r="I53" t="n">
-        <v>0.84796</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0.0009399999999999409</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0.1108542855795015</v>
+        <v>-0.924205778915019</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2728,37 +2302,29 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.84875</v>
+        <v>0.8489</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0.84796</v>
       </c>
       <c r="H54" t="n">
-        <v>200</v>
+        <v>0.0009399999999999409</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8489</v>
-      </c>
-      <c r="J54" t="n">
-        <v>-0.0001499999999999835</v>
-      </c>
-      <c r="K54" t="n">
-        <v>-0.01766992578630975</v>
+        <v>0.1108542855795015</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46129</v>
+        <v>46128</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2771,37 +2337,29 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.84767</v>
+        <v>0.84875</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0.8489</v>
       </c>
       <c r="H55" t="n">
-        <v>200</v>
+        <v>-0.0001499999999999835</v>
       </c>
       <c r="I55" t="n">
-        <v>0.84875</v>
-      </c>
-      <c r="J55" t="n">
-        <v>-0.00107999999999997</v>
-      </c>
-      <c r="K55" t="n">
-        <v>-0.1272459499263587</v>
+        <v>-0.01766992578630975</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46104</v>
+        <v>46129</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2810,41 +2368,33 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.74526</v>
+        <v>0.84767</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0.84875</v>
       </c>
       <c r="H56" t="n">
-        <v>200</v>
+        <v>-0.00107999999999997</v>
       </c>
       <c r="I56" t="n">
-        <v>0.74526</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+        <v>-0.1272459499263587</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46105</v>
+        <v>46132</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2853,41 +2403,33 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.74785</v>
+        <v>0.85034</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0.84767</v>
       </c>
       <c r="H57" t="n">
-        <v>200</v>
+        <v>0.00266999999999995</v>
       </c>
       <c r="I57" t="n">
-        <v>0.74526</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0.002589999999999981</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0.3475297211711324</v>
+        <v>0.3149810657449184</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46106</v>
+        <v>46133</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2896,41 +2438,33 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.7467</v>
+        <v>0.84983</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0.85034</v>
       </c>
       <c r="H58" t="n">
-        <v>200</v>
+        <v>-0.0005100000000000104</v>
       </c>
       <c r="I58" t="n">
-        <v>0.74785</v>
-      </c>
-      <c r="J58" t="n">
-        <v>-0.001149999999999984</v>
-      </c>
-      <c r="K58" t="n">
-        <v>-0.1537741525707006</v>
+        <v>-0.05997600959616276</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46107</v>
+        <v>46105</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2943,37 +2477,29 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.74976</v>
+        <v>0.74785</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0.74785</v>
       </c>
       <c r="H59" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7467</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0.003059999999999952</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0.4098031337886636</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2986,37 +2512,29 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.75297</v>
+        <v>0.7467</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0.74785</v>
       </c>
       <c r="H60" t="n">
-        <v>200</v>
+        <v>-0.001149999999999984</v>
       </c>
       <c r="I60" t="n">
-        <v>0.74976</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0.003210000000000046</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0.4281370038412354</v>
+        <v>-0.1537741525707006</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46111</v>
+        <v>46107</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3029,37 +2547,29 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.75586</v>
+        <v>0.74976</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0.7467</v>
       </c>
       <c r="H61" t="n">
-        <v>200</v>
+        <v>0.003059999999999952</v>
       </c>
       <c r="I61" t="n">
-        <v>0.75297</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.002889999999999948</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0.3838134321420439</v>
+        <v>0.4098031337886636</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46112</v>
+        <v>46108</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3072,37 +2582,29 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.7552</v>
+        <v>0.75297</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0.74976</v>
       </c>
       <c r="H62" t="n">
-        <v>200</v>
+        <v>0.003210000000000046</v>
       </c>
       <c r="I62" t="n">
-        <v>0.75586</v>
-      </c>
-      <c r="J62" t="n">
-        <v>-0.0006599999999999939</v>
-      </c>
-      <c r="K62" t="n">
-        <v>-0.08731775725663403</v>
+        <v>0.4281370038412354</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>46113</v>
+        <v>46111</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3115,37 +2617,29 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.75065</v>
+        <v>0.75586</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0.75297</v>
       </c>
       <c r="H63" t="n">
-        <v>200</v>
+        <v>0.002889999999999948</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7552</v>
-      </c>
-      <c r="J63" t="n">
-        <v>-0.004549999999999943</v>
-      </c>
-      <c r="K63" t="n">
-        <v>-0.6024894067796536</v>
+        <v>0.3838134321420439</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46114</v>
+        <v>46112</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3158,37 +2652,29 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.75708</v>
+        <v>0.7552</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0.75586</v>
       </c>
       <c r="H64" t="n">
-        <v>200</v>
+        <v>-0.0006599999999999939</v>
       </c>
       <c r="I64" t="n">
-        <v>0.75065</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0.006429999999999936</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0.8565909545060861</v>
+        <v>-0.08731775725663403</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3201,37 +2687,29 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.75502</v>
+        <v>0.75065</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0.7552</v>
       </c>
       <c r="H65" t="n">
-        <v>200</v>
+        <v>-0.004549999999999943</v>
       </c>
       <c r="I65" t="n">
-        <v>0.75708</v>
-      </c>
-      <c r="J65" t="n">
-        <v>-0.002059999999999951</v>
-      </c>
-      <c r="K65" t="n">
-        <v>-0.272098060971093</v>
+        <v>-0.6024894067796536</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46120</v>
+        <v>46114</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3244,37 +2722,29 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.74229</v>
+        <v>0.75708</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0.75065</v>
       </c>
       <c r="H66" t="n">
-        <v>200</v>
+        <v>0.006429999999999936</v>
       </c>
       <c r="I66" t="n">
-        <v>0.75502</v>
-      </c>
-      <c r="J66" t="n">
-        <v>-0.01273000000000002</v>
-      </c>
-      <c r="K66" t="n">
-        <v>-1.686048051707242</v>
+        <v>0.8565909545060861</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46121</v>
+        <v>46119</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3287,37 +2757,29 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.745</v>
+        <v>0.75502</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0.75708</v>
       </c>
       <c r="H67" t="n">
-        <v>200</v>
+        <v>-0.002059999999999951</v>
       </c>
       <c r="I67" t="n">
-        <v>0.74229</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0.00270999999999999</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0.3650864217489108</v>
+        <v>-0.272098060971093</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46122</v>
+        <v>46120</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3330,37 +2792,29 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.74379</v>
+        <v>0.74229</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0.75502</v>
       </c>
       <c r="H68" t="n">
-        <v>200</v>
+        <v>-0.01273000000000002</v>
       </c>
       <c r="I68" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="J68" t="n">
-        <v>-0.001210000000000044</v>
-      </c>
-      <c r="K68" t="n">
-        <v>-0.1624161073825563</v>
+        <v>-1.686048051707242</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46125</v>
+        <v>46121</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3373,37 +2827,29 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.7451</v>
+        <v>0.745</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0.74229</v>
       </c>
       <c r="H69" t="n">
-        <v>200</v>
+        <v>0.00270999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>0.74379</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0.001310000000000033</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0.1761249815136038</v>
+        <v>0.3650864217489108</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46126</v>
+        <v>46122</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -3416,37 +2862,29 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.73699</v>
+        <v>0.74379</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0.745</v>
       </c>
       <c r="H70" t="n">
-        <v>200</v>
+        <v>-0.001210000000000044</v>
       </c>
       <c r="I70" t="n">
-        <v>0.7451</v>
-      </c>
-      <c r="J70" t="n">
-        <v>-0.008109999999999951</v>
-      </c>
-      <c r="K70" t="n">
-        <v>-1.088444504093404</v>
+        <v>-0.1624161073825563</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46127</v>
+        <v>46125</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3459,37 +2897,29 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.73799</v>
+        <v>0.7451</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0.74379</v>
       </c>
       <c r="H71" t="n">
-        <v>200</v>
+        <v>0.001310000000000033</v>
       </c>
       <c r="I71" t="n">
-        <v>0.73699</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0.001000000000000001</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0.1356870513846865</v>
+        <v>0.1761249815136038</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46128</v>
+        <v>46126</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3502,37 +2932,29 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.73836</v>
+        <v>0.73699</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0.7451</v>
       </c>
       <c r="H72" t="n">
-        <v>200</v>
+        <v>-0.008109999999999951</v>
       </c>
       <c r="I72" t="n">
-        <v>0.73799</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0.0003699999999999815</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0.05013618070705313</v>
+        <v>-1.088444504093404</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46129</v>
+        <v>46127</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3545,37 +2967,29 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.7389</v>
+        <v>0.73799</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0.73699</v>
       </c>
       <c r="H73" t="n">
-        <v>200</v>
+        <v>0.001000000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>0.73836</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0.0005399999999999849</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0.07313505607020761</v>
+        <v>0.1356870513846865</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46104</v>
+        <v>46128</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3584,41 +2998,33 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>93.22</v>
+        <v>0.73836</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0.73799</v>
       </c>
       <c r="H74" t="n">
-        <v>200</v>
+        <v>0.0003699999999999815</v>
       </c>
       <c r="I74" t="n">
-        <v>93.22</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+        <v>0.05013618070705313</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46105</v>
+        <v>46129</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -3627,41 +3033,33 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>93.84999999999999</v>
+        <v>0.7389</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0.73836</v>
       </c>
       <c r="H75" t="n">
-        <v>200</v>
+        <v>0.0005399999999999849</v>
       </c>
       <c r="I75" t="n">
-        <v>93.22</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0.6299999999999955</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0.6758206393477746</v>
+        <v>0.07313505607020761</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46106</v>
+        <v>46132</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3670,41 +3068,33 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>93.94</v>
+        <v>0.7401799999999999</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0.7389</v>
       </c>
       <c r="H76" t="n">
-        <v>200</v>
+        <v>0.001279999999999948</v>
       </c>
       <c r="I76" t="n">
-        <v>93.84999999999999</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0.09000000000000341</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0.095897709110286</v>
+        <v>0.1732304777371698</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46107</v>
+        <v>46133</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3713,41 +3103,33 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>94.12</v>
+        <v>0.73965</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0.7401799999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>200</v>
+        <v>-0.0005299999999999194</v>
       </c>
       <c r="I77" t="n">
-        <v>93.94</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0.1800000000000068</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0.1916116670215104</v>
+        <v>-0.07160420438270683</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46108</v>
+        <v>46105</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3760,37 +3142,29 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>94.81</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>93.84999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>94.12</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0.6899999999999977</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0.7331066723331893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46111</v>
+        <v>46106</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3803,37 +3177,29 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>94.70999999999999</v>
+        <v>93.94</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>93.84999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>200</v>
+        <v>0.09000000000000341</v>
       </c>
       <c r="I79" t="n">
-        <v>94.81</v>
-      </c>
-      <c r="J79" t="n">
-        <v>-0.1000000000000085</v>
-      </c>
-      <c r="K79" t="n">
-        <v>-0.1054741061069597</v>
+        <v>0.095897709110286</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46112</v>
+        <v>46107</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3846,37 +3212,29 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>93.83</v>
+        <v>94.12</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>93.94</v>
       </c>
       <c r="H80" t="n">
-        <v>200</v>
+        <v>0.1800000000000068</v>
       </c>
       <c r="I80" t="n">
-        <v>94.70999999999999</v>
-      </c>
-      <c r="J80" t="n">
-        <v>-0.8799999999999955</v>
-      </c>
-      <c r="K80" t="n">
-        <v>-0.9291521486643392</v>
+        <v>0.1916116670215104</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46113</v>
+        <v>46108</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3889,37 +3247,29 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>93.43000000000001</v>
+        <v>94.81</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>94.12</v>
       </c>
       <c r="H81" t="n">
-        <v>200</v>
+        <v>0.6899999999999977</v>
       </c>
       <c r="I81" t="n">
-        <v>93.83</v>
-      </c>
-      <c r="J81" t="n">
-        <v>-0.3999999999999915</v>
-      </c>
-      <c r="K81" t="n">
-        <v>-0.4263028882020585</v>
+        <v>0.7331066723331893</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46114</v>
+        <v>46111</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3932,37 +3282,29 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>93.09999999999999</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>94.81</v>
       </c>
       <c r="H82" t="n">
-        <v>200</v>
+        <v>-0.1000000000000085</v>
       </c>
       <c r="I82" t="n">
-        <v>93.43000000000001</v>
-      </c>
-      <c r="J82" t="n">
-        <v>-0.3300000000000125</v>
-      </c>
-      <c r="K82" t="n">
-        <v>-0.353205608476948</v>
+        <v>-0.1054741061069597</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46119</v>
+        <v>46112</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -3975,37 +3317,29 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>93.01000000000001</v>
+        <v>93.83</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>94.70999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>200</v>
+        <v>-0.8799999999999955</v>
       </c>
       <c r="I83" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="J83" t="n">
-        <v>-0.0899999999999892</v>
-      </c>
-      <c r="K83" t="n">
-        <v>-0.0966702470461753</v>
+        <v>-0.9291521486643392</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46120</v>
+        <v>46113</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -4018,37 +3352,29 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>92.22</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>93.83</v>
       </c>
       <c r="H84" t="n">
-        <v>200</v>
+        <v>-0.3999999999999915</v>
       </c>
       <c r="I84" t="n">
-        <v>93.01000000000001</v>
-      </c>
-      <c r="J84" t="n">
-        <v>-0.7900000000000063</v>
-      </c>
-      <c r="K84" t="n">
-        <v>-0.8493710353725472</v>
+        <v>-0.4263028882020585</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46121</v>
+        <v>46114</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -4061,37 +3387,29 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>92.66</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>93.43000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>200</v>
+        <v>-0.3300000000000125</v>
       </c>
       <c r="I85" t="n">
-        <v>92.22</v>
-      </c>
-      <c r="J85" t="n">
-        <v>0.4399999999999977</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0.4771199306007349</v>
+        <v>-0.353205608476948</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46122</v>
+        <v>46119</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -4104,37 +3422,29 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>92.89</v>
+        <v>93.01000000000001</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>93.09999999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>200</v>
+        <v>-0.0899999999999892</v>
       </c>
       <c r="I86" t="n">
-        <v>92.66</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0.230000000000004</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0.2482192963522599</v>
+        <v>-0.0966702470461753</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46125</v>
+        <v>46120</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -4147,37 +3457,29 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>93.33</v>
+        <v>92.22</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>93.01000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>200</v>
+        <v>-0.7900000000000063</v>
       </c>
       <c r="I87" t="n">
-        <v>92.89</v>
-      </c>
-      <c r="J87" t="n">
-        <v>0.4399999999999977</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0.4736785445150153</v>
+        <v>-0.8493710353725472</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46126</v>
+        <v>46121</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -4190,37 +3492,29 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>93.09</v>
+        <v>92.66</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>92.22</v>
       </c>
       <c r="H88" t="n">
-        <v>200</v>
+        <v>0.4399999999999977</v>
       </c>
       <c r="I88" t="n">
-        <v>93.33</v>
-      </c>
-      <c r="J88" t="n">
-        <v>-0.2399999999999949</v>
-      </c>
-      <c r="K88" t="n">
-        <v>-0.2571520411443211</v>
+        <v>0.4771199306007349</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46127</v>
+        <v>46122</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -4233,37 +3527,29 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>93.44</v>
+        <v>92.89</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>92.66</v>
       </c>
       <c r="H89" t="n">
-        <v>200</v>
+        <v>0.230000000000004</v>
       </c>
       <c r="I89" t="n">
-        <v>93.09</v>
-      </c>
-      <c r="J89" t="n">
-        <v>0.3499999999999943</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0.3759802341819684</v>
+        <v>0.2482192963522599</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46128</v>
+        <v>46125</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -4276,37 +3562,29 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>93.23999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>92.89</v>
       </c>
       <c r="H90" t="n">
-        <v>200</v>
+        <v>0.4399999999999977</v>
       </c>
       <c r="I90" t="n">
-        <v>93.44</v>
-      </c>
-      <c r="J90" t="n">
-        <v>-0.2000000000000028</v>
-      </c>
-      <c r="K90" t="n">
-        <v>-0.214041095890414</v>
+        <v>0.4736785445150153</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46129</v>
+        <v>46126</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -4319,37 +3597,29 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>92.81999999999999</v>
+        <v>93.09</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>93.33</v>
       </c>
       <c r="H91" t="n">
-        <v>200</v>
+        <v>-0.2399999999999949</v>
       </c>
       <c r="I91" t="n">
-        <v>93.23999999999999</v>
-      </c>
-      <c r="J91" t="n">
-        <v>-0.4200000000000017</v>
-      </c>
-      <c r="K91" t="n">
-        <v>-0.4504504504504523</v>
+        <v>-0.2571520411443211</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46104</v>
+        <v>46127</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -4358,41 +3628,33 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>158.55</v>
+        <v>93.44</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>93.09</v>
       </c>
       <c r="H92" t="n">
-        <v>200</v>
+        <v>0.3499999999999943</v>
       </c>
       <c r="I92" t="n">
-        <v>158.55</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
+        <v>0.3759802341819684</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46105</v>
+        <v>46128</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -4401,41 +3663,33 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>158.93</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>93.44</v>
       </c>
       <c r="H93" t="n">
-        <v>200</v>
+        <v>-0.2000000000000028</v>
       </c>
       <c r="I93" t="n">
-        <v>158.55</v>
-      </c>
-      <c r="J93" t="n">
-        <v>0.3799999999999955</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0.239672027751495</v>
+        <v>-0.214041095890414</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46106</v>
+        <v>46129</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -4444,41 +3698,33 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>158.96</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>93.23999999999999</v>
       </c>
       <c r="H94" t="n">
-        <v>200</v>
+        <v>-0.4200000000000017</v>
       </c>
       <c r="I94" t="n">
-        <v>158.93</v>
-      </c>
-      <c r="J94" t="n">
-        <v>0.03000000000000114</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0.01887623482036188</v>
+        <v>-0.4504504504504523</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46107</v>
+        <v>46132</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -4487,41 +3733,33 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>159.62</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>92.81999999999999</v>
       </c>
       <c r="H95" t="n">
-        <v>200</v>
+        <v>0.25</v>
       </c>
       <c r="I95" t="n">
-        <v>158.96</v>
-      </c>
-      <c r="J95" t="n">
-        <v>0.6599999999999966</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0.4151987921489662</v>
+        <v>0.2693385046326223</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46108</v>
+        <v>46133</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -4530,41 +3768,33 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>159.9</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>93.06999999999999</v>
       </c>
       <c r="H96" t="n">
-        <v>200</v>
+        <v>0.4400000000000119</v>
       </c>
       <c r="I96" t="n">
-        <v>159.62</v>
-      </c>
-      <c r="J96" t="n">
-        <v>0.2800000000000011</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0.1754166144593416</v>
+        <v>0.4727624368754829</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46111</v>
+        <v>46105</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -4577,37 +3807,29 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>159.46</v>
+        <v>158.93</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>158.93</v>
       </c>
       <c r="H97" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>159.9</v>
-      </c>
-      <c r="J97" t="n">
-        <v>-0.4399999999999977</v>
-      </c>
-      <c r="K97" t="n">
-        <v>-0.2751719824890542</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46112</v>
+        <v>46106</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -4620,37 +3842,29 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>159.5</v>
+        <v>158.96</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>158.93</v>
       </c>
       <c r="H98" t="n">
-        <v>200</v>
+        <v>0.03000000000000114</v>
       </c>
       <c r="I98" t="n">
-        <v>159.46</v>
-      </c>
-      <c r="J98" t="n">
-        <v>0.03999999999999204</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0.02508466072995864</v>
+        <v>0.01887623482036188</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -4663,37 +3877,29 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>158.32</v>
+        <v>159.62</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>158.96</v>
       </c>
       <c r="H99" t="n">
-        <v>200</v>
+        <v>0.6599999999999966</v>
       </c>
       <c r="I99" t="n">
-        <v>159.5</v>
-      </c>
-      <c r="J99" t="n">
-        <v>-1.180000000000007</v>
-      </c>
-      <c r="K99" t="n">
-        <v>-0.7398119122257096</v>
+        <v>0.4151987921489662</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46114</v>
+        <v>46108</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -4706,37 +3912,29 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>159.6</v>
+        <v>159.9</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>159.62</v>
       </c>
       <c r="H100" t="n">
-        <v>200</v>
+        <v>0.2800000000000011</v>
       </c>
       <c r="I100" t="n">
-        <v>158.32</v>
-      </c>
-      <c r="J100" t="n">
-        <v>1.280000000000001</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0.8084891359272367</v>
+        <v>0.1754166144593416</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46119</v>
+        <v>46111</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -4749,37 +3947,29 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>159.84</v>
+        <v>159.46</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>159.9</v>
       </c>
       <c r="H101" t="n">
-        <v>200</v>
+        <v>-0.4399999999999977</v>
       </c>
       <c r="I101" t="n">
-        <v>159.6</v>
-      </c>
-      <c r="J101" t="n">
-        <v>0.2400000000000091</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0.1503759398496298</v>
+        <v>-0.2751719824890542</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46120</v>
+        <v>46112</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -4792,37 +3982,29 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>158.15</v>
+        <v>159.5</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>159.46</v>
       </c>
       <c r="H102" t="n">
-        <v>200</v>
+        <v>0.03999999999999204</v>
       </c>
       <c r="I102" t="n">
-        <v>159.84</v>
-      </c>
-      <c r="J102" t="n">
-        <v>-1.689999999999998</v>
-      </c>
-      <c r="K102" t="n">
-        <v>-1.057307307307306</v>
+        <v>0.02508466072995864</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46121</v>
+        <v>46113</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -4835,37 +4017,29 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>158.92</v>
+        <v>158.32</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>159.5</v>
       </c>
       <c r="H103" t="n">
-        <v>200</v>
+        <v>-1.180000000000007</v>
       </c>
       <c r="I103" t="n">
-        <v>158.15</v>
-      </c>
-      <c r="J103" t="n">
-        <v>0.7699999999999818</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0.4868795447359986</v>
+        <v>-0.7398119122257096</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46122</v>
+        <v>46114</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -4878,37 +4052,29 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>159.19</v>
+        <v>159.6</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>158.32</v>
       </c>
       <c r="H104" t="n">
-        <v>200</v>
+        <v>1.280000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>158.92</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0.2700000000000102</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0.1698968034231124</v>
+        <v>0.8084891359272367</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46125</v>
+        <v>46119</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -4921,37 +4087,29 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>159.83</v>
+        <v>159.84</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>159.6</v>
       </c>
       <c r="H105" t="n">
-        <v>200</v>
+        <v>0.2400000000000091</v>
       </c>
       <c r="I105" t="n">
-        <v>159.19</v>
-      </c>
-      <c r="J105" t="n">
-        <v>0.6400000000000148</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0.4020353037251177</v>
+        <v>0.1503759398496298</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46126</v>
+        <v>46120</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -4964,37 +4122,29 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>158.85</v>
+        <v>158.15</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>159.84</v>
       </c>
       <c r="H106" t="n">
-        <v>200</v>
+        <v>-1.689999999999998</v>
       </c>
       <c r="I106" t="n">
-        <v>159.83</v>
-      </c>
-      <c r="J106" t="n">
-        <v>-0.9800000000000182</v>
-      </c>
-      <c r="K106" t="n">
-        <v>-0.6131514734405419</v>
+        <v>-1.057307307307306</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46127</v>
+        <v>46121</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -5007,37 +4157,29 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>159.09</v>
+        <v>158.92</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>158.15</v>
       </c>
       <c r="H107" t="n">
-        <v>200</v>
+        <v>0.7699999999999818</v>
       </c>
       <c r="I107" t="n">
-        <v>158.85</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0.2400000000000091</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0.1510859301227631</v>
+        <v>0.4868795447359986</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46128</v>
+        <v>46122</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -5050,75 +4192,269 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>158.98</v>
+        <v>159.19</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46131.63921188703</v>
+        <v>46134.56990716779</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>158.92</v>
       </c>
       <c r="H108" t="n">
-        <v>200</v>
+        <v>0.2700000000000102</v>
       </c>
       <c r="I108" t="n">
-        <v>159.09</v>
-      </c>
-      <c r="J108" t="n">
-        <v>-0.1100000000000136</v>
-      </c>
-      <c r="K108" t="n">
-        <v>-0.06914325224716428</v>
+        <v>0.1698968034231124</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>159.83</v>
+      </c>
+      <c r="E109" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>159.19</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.6400000000000148</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.4020353037251177</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>158.85</v>
+      </c>
+      <c r="E110" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>159.83</v>
+      </c>
+      <c r="H110" t="n">
+        <v>-0.9800000000000182</v>
+      </c>
+      <c r="I110" t="n">
+        <v>-0.6131514734405419</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>159.09</v>
+      </c>
+      <c r="E111" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>158.85</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.2400000000000091</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.1510859301227631</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>158.98</v>
+      </c>
+      <c r="E112" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>159.09</v>
+      </c>
+      <c r="H112" t="n">
+        <v>-0.1100000000000136</v>
+      </c>
+      <c r="I112" t="n">
+        <v>-0.06914325224716428</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
         <v>46129</v>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
         <is>
           <t>JPY</t>
         </is>
       </c>
-      <c r="D109" t="n">
+      <c r="D113" t="n">
         <v>159.13</v>
       </c>
-      <c r="E109" s="1" t="n">
-        <v>46131.63921188703</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>fx_20260419_152027</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="H109" t="n">
-        <v>200</v>
-      </c>
-      <c r="I109" t="n">
+      <c r="E113" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
         <v>158.98</v>
       </c>
-      <c r="J109" t="n">
+      <c r="H113" t="n">
         <v>0.1500000000000057</v>
       </c>
-      <c r="K109" t="n">
+      <c r="I113" t="n">
         <v>0.09435149075355749</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>158.91</v>
+      </c>
+      <c r="E114" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>159.13</v>
+      </c>
+      <c r="H114" t="n">
+        <v>-0.2199999999999989</v>
+      </c>
+      <c r="I114" t="n">
+        <v>-0.1382517438572229</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>159.04</v>
+      </c>
+      <c r="E115" s="1" t="n">
+        <v>46134.56990716779</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>fx_20260422_134039</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>158.91</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.1299999999999955</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.08180731231514407</v>
       </c>
     </row>
   </sheetData>
